--- a/tests/fixtures/browser/spike/gaps.xlsx
+++ b/tests/fixtures/browser/spike/gaps.xlsx
@@ -84,14 +84,14 @@
           <t xml:space="preserve">a1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">c1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">c2</t>
         </is>
